--- a/public/modelos/biblioteca-v2/PCM-MAN-015_Auditoria-5S-e-Melhorias_R00.xlsx
+++ b/public/modelos/biblioteca-v2/PCM-MAN-015_Auditoria-5S-e-Melhorias_R00.xlsx
@@ -683,17 +683,6 @@
       <left style="thin">
         <color rgb="000B2A5B"/>
       </left>
-      <right style="thin">
-        <color rgb="000B2A5B"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="00D3DEEC"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="000B2A5B"/>
-      </left>
       <bottom style="thin">
         <color rgb="00D3DEEC"/>
       </bottom>
@@ -759,6 +748,17 @@
       </right>
       <bottom style="thin">
         <color rgb="000B2A5B"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000B2A5B"/>
+      </left>
+      <right style="thin">
+        <color rgb="000B2A5B"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00D3DEEC"/>
       </bottom>
     </border>
     <border>
@@ -977,7 +977,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -1323,52 +1323,50 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1377,13 +1375,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1661,37 +1659,37 @@
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
-        <t>Responsável.</t>
+        <t>TAG. Digite como texto (preserva zeros à esquerda). Exemplo: 00123.</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>Equipamento.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
-        <t>Setor.</t>
+        <t>Família de equipamento. Escolha na lista (preencha antes a aba Cadastros).</t>
       </text>
     </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
+    <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>TAG. Digite como texto (preserva zeros à esquerda). Exemplo: 00123.</t>
+        <t>Setor. Escolha na lista (preencha antes a aba Cadastros).</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
-        <t>Equipamento.</t>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0" shapeId="0">
-      <text>
-        <t>Família de equipamento. Escolha na lista (preencha antes a aba Cadastros).</t>
+        <t>Responsável.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
-        <t>Setor. Escolha na lista (preencha antes a aba Cadastros).</t>
+        <t>Família de equipamento.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
-        <t>Família de equipamento.</t>
+        <t>Setor.</t>
       </text>
     </comment>
   </commentList>
@@ -1905,11 +1903,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>76200</colOff>
+      <colOff>695325</colOff>
       <row>0</row>
-      <rowOff>85725</rowOff>
+      <rowOff>47625</rowOff>
     </from>
-    <ext cx="1895475" cy="561975"/>
+    <ext cx="2162175" cy="647700"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1961,43 +1959,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tb_pcm_pessoas" displayName="tb_pcm_pessoas" ref="A4:A29" headerRowCount="1">
-  <autoFilter ref="A4:A29"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="nome_pessoa"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tb_pcm_ativos" displayName="tb_pcm_ativos" ref="A4:D29" headerRowCount="1">
+  <autoFilter ref="A4:D29"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="tag"/>
+    <tableColumn id="2" name="descricao_ativo"/>
+    <tableColumn id="3" name="familia"/>
+    <tableColumn id="4" name="setor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="C4:C29" headerRowCount="1">
-  <autoFilter ref="C4:C29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tb_pcm_pessoas" displayName="tb_pcm_pessoas" ref="F4:F29" headerRowCount="1">
+  <autoFilter ref="F4:F29"/>
   <tableColumns count="1">
-    <tableColumn id="3" name="nome_setor"/>
+    <tableColumn id="6" name="nome_pessoa"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_pcm_ativos" displayName="tb_pcm_ativos" ref="E4:H29" headerRowCount="1">
-  <autoFilter ref="E4:H29"/>
-  <tableColumns count="4">
-    <tableColumn id="5" name="tag"/>
-    <tableColumn id="6" name="descricao_ativo"/>
-    <tableColumn id="7" name="familia"/>
-    <tableColumn id="8" name="setor"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="H4:H29" headerRowCount="1">
+  <autoFilter ref="H4:H29"/>
+  <tableColumns count="1">
+    <tableColumn id="8" name="nome_familia"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_familias" displayName="tb_pcm_familias" ref="J4:J29" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tb_pcm_setores" displayName="tb_pcm_setores" ref="J4:J29" headerRowCount="1">
   <autoFilter ref="J4:J29"/>
   <tableColumns count="1">
-    <tableColumn id="10" name="nome_familia"/>
+    <tableColumn id="10" name="nome_setor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="0"/>
 </table>
@@ -2656,7 +2654,7 @@
       </c>
       <c r="D19" s="28" t="inlineStr">
         <is>
-          <t>Cadastre uma vez as pessoas, os setores, TAG, equipamento, família e setor, as famílias de equipamento. Eles aparecem nas setas ▼ das outras abas.</t>
+          <t>Cadastre uma vez TAG, equipamento, família e setor, as pessoas, as famílias de equipamento, os setores. Eles aparecem nas setas ▼ das outras abas.</t>
         </is>
       </c>
       <c r="E19" s="29" t="n"/>
@@ -5981,26 +5979,26 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="3" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="3" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="155" t="n"/>
-      <c r="B1" s="84" t="inlineStr">
+      <c r="A1" s="39" t="n"/>
+      <c r="B1" s="40" t="n"/>
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Cadastros</t>
         </is>
       </c>
-      <c r="C1" s="42" t="n"/>
       <c r="D1" s="42" t="n"/>
       <c r="E1" s="42" t="n"/>
       <c r="F1" s="42" t="n"/>
@@ -6013,13 +6011,13 @@
       <c r="J1" s="40" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="156" t="n"/>
-      <c r="B2" s="46" t="inlineStr">
+      <c r="A2" s="44" t="n"/>
+      <c r="B2" s="45" t="n"/>
+      <c r="C2" s="46" t="inlineStr">
         <is>
           <t>Objetivo: Cadastre aqui os itens usados nas listas (▼) das outras abas.</t>
         </is>
       </c>
-      <c r="C2" s="47" t="n"/>
       <c r="D2" s="47" t="n"/>
       <c r="E2" s="47" t="n"/>
       <c r="F2" s="47" t="n"/>
@@ -6032,306 +6030,306 @@
       <c r="J2" s="45" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="157" t="inlineStr">
+      <c r="A3" s="155" t="inlineStr">
+        <is>
+          <t>TAG</t>
+        </is>
+      </c>
+      <c r="B3" s="156" t="inlineStr">
+        <is>
+          <t>Equipamento</t>
+        </is>
+      </c>
+      <c r="C3" s="156" t="inlineStr">
+        <is>
+          <t>Família de equipamento ▼</t>
+        </is>
+      </c>
+      <c r="D3" s="157" t="inlineStr">
+        <is>
+          <t>Setor ▼</t>
+        </is>
+      </c>
+      <c r="F3" s="158" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="C3" s="157" t="inlineStr">
+      <c r="H3" s="158" t="inlineStr">
+        <is>
+          <t>Família de equipamento</t>
+        </is>
+      </c>
+      <c r="J3" s="158" t="inlineStr">
         <is>
           <t>Setor</t>
         </is>
       </c>
-      <c r="E3" s="158" t="inlineStr">
-        <is>
-          <t>TAG</t>
-        </is>
-      </c>
-      <c r="F3" s="159" t="inlineStr">
-        <is>
-          <t>Equipamento</t>
-        </is>
-      </c>
-      <c r="G3" s="159" t="inlineStr">
-        <is>
-          <t>Família de equipamento ▼</t>
-        </is>
-      </c>
-      <c r="H3" s="160" t="inlineStr">
-        <is>
-          <t>Setor ▼</t>
-        </is>
-      </c>
-      <c r="J3" s="157" t="inlineStr">
-        <is>
-          <t>Família de equipamento</t>
-        </is>
-      </c>
     </row>
     <row r="4" hidden="1">
-      <c r="A4" s="161" t="inlineStr">
+      <c r="A4" s="159" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="B4" s="159" t="inlineStr">
+        <is>
+          <t>descricao_ativo</t>
+        </is>
+      </c>
+      <c r="C4" s="159" t="inlineStr">
+        <is>
+          <t>familia</t>
+        </is>
+      </c>
+      <c r="D4" s="159" t="inlineStr">
+        <is>
+          <t>setor</t>
+        </is>
+      </c>
+      <c r="F4" s="159" t="inlineStr">
         <is>
           <t>nome_pessoa</t>
         </is>
       </c>
-      <c r="C4" s="161" t="inlineStr">
+      <c r="H4" s="159" t="inlineStr">
+        <is>
+          <t>nome_familia</t>
+        </is>
+      </c>
+      <c r="J4" s="159" t="inlineStr">
         <is>
           <t>nome_setor</t>
         </is>
       </c>
-      <c r="E4" s="161" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="F4" s="161" t="inlineStr">
-        <is>
-          <t>descricao_ativo</t>
-        </is>
-      </c>
-      <c r="G4" s="161" t="inlineStr">
-        <is>
-          <t>familia</t>
-        </is>
-      </c>
-      <c r="H4" s="161" t="inlineStr">
-        <is>
-          <t>setor</t>
-        </is>
-      </c>
-      <c r="J4" s="161" t="inlineStr">
-        <is>
-          <t>nome_familia</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="162" t="n"/>
-      <c r="C5" s="162" t="n"/>
-      <c r="E5" s="163" t="n"/>
-      <c r="F5" s="164" t="n"/>
-      <c r="G5" s="164" t="n"/>
-      <c r="H5" s="165" t="n"/>
-      <c r="J5" s="162" t="n"/>
+      <c r="A5" s="160" t="n"/>
+      <c r="B5" s="161" t="n"/>
+      <c r="C5" s="161" t="n"/>
+      <c r="D5" s="162" t="n"/>
+      <c r="F5" s="163" t="n"/>
+      <c r="H5" s="163" t="n"/>
+      <c r="J5" s="163" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="162" t="n"/>
-      <c r="C6" s="162" t="n"/>
-      <c r="E6" s="163" t="n"/>
-      <c r="F6" s="164" t="n"/>
-      <c r="G6" s="164" t="n"/>
-      <c r="H6" s="165" t="n"/>
-      <c r="J6" s="162" t="n"/>
+      <c r="A6" s="160" t="n"/>
+      <c r="B6" s="161" t="n"/>
+      <c r="C6" s="161" t="n"/>
+      <c r="D6" s="162" t="n"/>
+      <c r="F6" s="163" t="n"/>
+      <c r="H6" s="163" t="n"/>
+      <c r="J6" s="163" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="162" t="n"/>
-      <c r="C7" s="162" t="n"/>
-      <c r="E7" s="163" t="n"/>
-      <c r="F7" s="164" t="n"/>
-      <c r="G7" s="164" t="n"/>
-      <c r="H7" s="165" t="n"/>
-      <c r="J7" s="162" t="n"/>
+      <c r="A7" s="160" t="n"/>
+      <c r="B7" s="161" t="n"/>
+      <c r="C7" s="161" t="n"/>
+      <c r="D7" s="162" t="n"/>
+      <c r="F7" s="163" t="n"/>
+      <c r="H7" s="163" t="n"/>
+      <c r="J7" s="163" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="162" t="n"/>
-      <c r="C8" s="162" t="n"/>
-      <c r="E8" s="163" t="n"/>
-      <c r="F8" s="164" t="n"/>
-      <c r="G8" s="164" t="n"/>
-      <c r="H8" s="165" t="n"/>
-      <c r="J8" s="162" t="n"/>
+      <c r="A8" s="160" t="n"/>
+      <c r="B8" s="161" t="n"/>
+      <c r="C8" s="161" t="n"/>
+      <c r="D8" s="162" t="n"/>
+      <c r="F8" s="163" t="n"/>
+      <c r="H8" s="163" t="n"/>
+      <c r="J8" s="163" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="162" t="n"/>
-      <c r="C9" s="162" t="n"/>
-      <c r="E9" s="163" t="n"/>
-      <c r="F9" s="164" t="n"/>
-      <c r="G9" s="164" t="n"/>
-      <c r="H9" s="165" t="n"/>
-      <c r="J9" s="162" t="n"/>
+      <c r="A9" s="160" t="n"/>
+      <c r="B9" s="161" t="n"/>
+      <c r="C9" s="161" t="n"/>
+      <c r="D9" s="162" t="n"/>
+      <c r="F9" s="163" t="n"/>
+      <c r="H9" s="163" t="n"/>
+      <c r="J9" s="163" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="162" t="n"/>
-      <c r="C10" s="162" t="n"/>
-      <c r="E10" s="163" t="n"/>
-      <c r="F10" s="164" t="n"/>
-      <c r="G10" s="164" t="n"/>
-      <c r="H10" s="165" t="n"/>
-      <c r="J10" s="162" t="n"/>
+      <c r="A10" s="160" t="n"/>
+      <c r="B10" s="161" t="n"/>
+      <c r="C10" s="161" t="n"/>
+      <c r="D10" s="162" t="n"/>
+      <c r="F10" s="163" t="n"/>
+      <c r="H10" s="163" t="n"/>
+      <c r="J10" s="163" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="162" t="n"/>
-      <c r="C11" s="162" t="n"/>
-      <c r="E11" s="163" t="n"/>
-      <c r="F11" s="164" t="n"/>
-      <c r="G11" s="164" t="n"/>
-      <c r="H11" s="165" t="n"/>
-      <c r="J11" s="162" t="n"/>
+      <c r="A11" s="160" t="n"/>
+      <c r="B11" s="161" t="n"/>
+      <c r="C11" s="161" t="n"/>
+      <c r="D11" s="162" t="n"/>
+      <c r="F11" s="163" t="n"/>
+      <c r="H11" s="163" t="n"/>
+      <c r="J11" s="163" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="162" t="n"/>
-      <c r="C12" s="162" t="n"/>
-      <c r="E12" s="163" t="n"/>
-      <c r="F12" s="164" t="n"/>
-      <c r="G12" s="164" t="n"/>
-      <c r="H12" s="165" t="n"/>
-      <c r="J12" s="162" t="n"/>
+      <c r="A12" s="160" t="n"/>
+      <c r="B12" s="161" t="n"/>
+      <c r="C12" s="161" t="n"/>
+      <c r="D12" s="162" t="n"/>
+      <c r="F12" s="163" t="n"/>
+      <c r="H12" s="163" t="n"/>
+      <c r="J12" s="163" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="162" t="n"/>
-      <c r="C13" s="162" t="n"/>
-      <c r="E13" s="163" t="n"/>
-      <c r="F13" s="164" t="n"/>
-      <c r="G13" s="164" t="n"/>
-      <c r="H13" s="165" t="n"/>
-      <c r="J13" s="162" t="n"/>
+      <c r="A13" s="160" t="n"/>
+      <c r="B13" s="161" t="n"/>
+      <c r="C13" s="161" t="n"/>
+      <c r="D13" s="162" t="n"/>
+      <c r="F13" s="163" t="n"/>
+      <c r="H13" s="163" t="n"/>
+      <c r="J13" s="163" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="162" t="n"/>
-      <c r="C14" s="162" t="n"/>
-      <c r="E14" s="163" t="n"/>
-      <c r="F14" s="164" t="n"/>
-      <c r="G14" s="164" t="n"/>
-      <c r="H14" s="165" t="n"/>
-      <c r="J14" s="162" t="n"/>
+      <c r="A14" s="160" t="n"/>
+      <c r="B14" s="161" t="n"/>
+      <c r="C14" s="161" t="n"/>
+      <c r="D14" s="162" t="n"/>
+      <c r="F14" s="163" t="n"/>
+      <c r="H14" s="163" t="n"/>
+      <c r="J14" s="163" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="162" t="n"/>
-      <c r="C15" s="162" t="n"/>
-      <c r="E15" s="163" t="n"/>
-      <c r="F15" s="164" t="n"/>
-      <c r="G15" s="164" t="n"/>
-      <c r="H15" s="165" t="n"/>
-      <c r="J15" s="162" t="n"/>
+      <c r="A15" s="160" t="n"/>
+      <c r="B15" s="161" t="n"/>
+      <c r="C15" s="161" t="n"/>
+      <c r="D15" s="162" t="n"/>
+      <c r="F15" s="163" t="n"/>
+      <c r="H15" s="163" t="n"/>
+      <c r="J15" s="163" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="162" t="n"/>
-      <c r="C16" s="162" t="n"/>
-      <c r="E16" s="163" t="n"/>
-      <c r="F16" s="164" t="n"/>
-      <c r="G16" s="164" t="n"/>
-      <c r="H16" s="165" t="n"/>
-      <c r="J16" s="162" t="n"/>
+      <c r="A16" s="160" t="n"/>
+      <c r="B16" s="161" t="n"/>
+      <c r="C16" s="161" t="n"/>
+      <c r="D16" s="162" t="n"/>
+      <c r="F16" s="163" t="n"/>
+      <c r="H16" s="163" t="n"/>
+      <c r="J16" s="163" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="162" t="n"/>
-      <c r="C17" s="162" t="n"/>
-      <c r="E17" s="163" t="n"/>
-      <c r="F17" s="164" t="n"/>
-      <c r="G17" s="164" t="n"/>
-      <c r="H17" s="165" t="n"/>
-      <c r="J17" s="162" t="n"/>
+      <c r="A17" s="160" t="n"/>
+      <c r="B17" s="161" t="n"/>
+      <c r="C17" s="161" t="n"/>
+      <c r="D17" s="162" t="n"/>
+      <c r="F17" s="163" t="n"/>
+      <c r="H17" s="163" t="n"/>
+      <c r="J17" s="163" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="162" t="n"/>
-      <c r="C18" s="162" t="n"/>
-      <c r="E18" s="163" t="n"/>
-      <c r="F18" s="164" t="n"/>
-      <c r="G18" s="164" t="n"/>
-      <c r="H18" s="165" t="n"/>
-      <c r="J18" s="162" t="n"/>
+      <c r="A18" s="160" t="n"/>
+      <c r="B18" s="161" t="n"/>
+      <c r="C18" s="161" t="n"/>
+      <c r="D18" s="162" t="n"/>
+      <c r="F18" s="163" t="n"/>
+      <c r="H18" s="163" t="n"/>
+      <c r="J18" s="163" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="162" t="n"/>
-      <c r="C19" s="162" t="n"/>
-      <c r="E19" s="163" t="n"/>
-      <c r="F19" s="164" t="n"/>
-      <c r="G19" s="164" t="n"/>
-      <c r="H19" s="165" t="n"/>
-      <c r="J19" s="162" t="n"/>
+      <c r="A19" s="160" t="n"/>
+      <c r="B19" s="161" t="n"/>
+      <c r="C19" s="161" t="n"/>
+      <c r="D19" s="162" t="n"/>
+      <c r="F19" s="163" t="n"/>
+      <c r="H19" s="163" t="n"/>
+      <c r="J19" s="163" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="162" t="n"/>
-      <c r="C20" s="162" t="n"/>
-      <c r="E20" s="163" t="n"/>
-      <c r="F20" s="164" t="n"/>
-      <c r="G20" s="164" t="n"/>
-      <c r="H20" s="165" t="n"/>
-      <c r="J20" s="162" t="n"/>
+      <c r="A20" s="160" t="n"/>
+      <c r="B20" s="161" t="n"/>
+      <c r="C20" s="161" t="n"/>
+      <c r="D20" s="162" t="n"/>
+      <c r="F20" s="163" t="n"/>
+      <c r="H20" s="163" t="n"/>
+      <c r="J20" s="163" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="162" t="n"/>
-      <c r="C21" s="162" t="n"/>
-      <c r="E21" s="163" t="n"/>
-      <c r="F21" s="164" t="n"/>
-      <c r="G21" s="164" t="n"/>
-      <c r="H21" s="165" t="n"/>
-      <c r="J21" s="162" t="n"/>
+      <c r="A21" s="160" t="n"/>
+      <c r="B21" s="161" t="n"/>
+      <c r="C21" s="161" t="n"/>
+      <c r="D21" s="162" t="n"/>
+      <c r="F21" s="163" t="n"/>
+      <c r="H21" s="163" t="n"/>
+      <c r="J21" s="163" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="162" t="n"/>
-      <c r="C22" s="162" t="n"/>
-      <c r="E22" s="163" t="n"/>
-      <c r="F22" s="164" t="n"/>
-      <c r="G22" s="164" t="n"/>
-      <c r="H22" s="165" t="n"/>
-      <c r="J22" s="162" t="n"/>
+      <c r="A22" s="160" t="n"/>
+      <c r="B22" s="161" t="n"/>
+      <c r="C22" s="161" t="n"/>
+      <c r="D22" s="162" t="n"/>
+      <c r="F22" s="163" t="n"/>
+      <c r="H22" s="163" t="n"/>
+      <c r="J22" s="163" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="162" t="n"/>
-      <c r="C23" s="162" t="n"/>
-      <c r="E23" s="163" t="n"/>
-      <c r="F23" s="164" t="n"/>
-      <c r="G23" s="164" t="n"/>
-      <c r="H23" s="165" t="n"/>
-      <c r="J23" s="162" t="n"/>
+      <c r="A23" s="160" t="n"/>
+      <c r="B23" s="161" t="n"/>
+      <c r="C23" s="161" t="n"/>
+      <c r="D23" s="162" t="n"/>
+      <c r="F23" s="163" t="n"/>
+      <c r="H23" s="163" t="n"/>
+      <c r="J23" s="163" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="162" t="n"/>
-      <c r="C24" s="162" t="n"/>
-      <c r="E24" s="163" t="n"/>
-      <c r="F24" s="164" t="n"/>
-      <c r="G24" s="164" t="n"/>
-      <c r="H24" s="165" t="n"/>
-      <c r="J24" s="162" t="n"/>
+      <c r="A24" s="160" t="n"/>
+      <c r="B24" s="161" t="n"/>
+      <c r="C24" s="161" t="n"/>
+      <c r="D24" s="162" t="n"/>
+      <c r="F24" s="163" t="n"/>
+      <c r="H24" s="163" t="n"/>
+      <c r="J24" s="163" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="162" t="n"/>
-      <c r="C25" s="162" t="n"/>
-      <c r="E25" s="163" t="n"/>
-      <c r="F25" s="164" t="n"/>
-      <c r="G25" s="164" t="n"/>
-      <c r="H25" s="165" t="n"/>
-      <c r="J25" s="162" t="n"/>
+      <c r="A25" s="160" t="n"/>
+      <c r="B25" s="161" t="n"/>
+      <c r="C25" s="161" t="n"/>
+      <c r="D25" s="162" t="n"/>
+      <c r="F25" s="163" t="n"/>
+      <c r="H25" s="163" t="n"/>
+      <c r="J25" s="163" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="162" t="n"/>
-      <c r="C26" s="162" t="n"/>
-      <c r="E26" s="163" t="n"/>
-      <c r="F26" s="164" t="n"/>
-      <c r="G26" s="164" t="n"/>
-      <c r="H26" s="165" t="n"/>
-      <c r="J26" s="162" t="n"/>
+      <c r="A26" s="160" t="n"/>
+      <c r="B26" s="161" t="n"/>
+      <c r="C26" s="161" t="n"/>
+      <c r="D26" s="162" t="n"/>
+      <c r="F26" s="163" t="n"/>
+      <c r="H26" s="163" t="n"/>
+      <c r="J26" s="163" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="162" t="n"/>
-      <c r="C27" s="162" t="n"/>
-      <c r="E27" s="163" t="n"/>
-      <c r="F27" s="164" t="n"/>
-      <c r="G27" s="164" t="n"/>
-      <c r="H27" s="165" t="n"/>
-      <c r="J27" s="162" t="n"/>
+      <c r="A27" s="160" t="n"/>
+      <c r="B27" s="161" t="n"/>
+      <c r="C27" s="161" t="n"/>
+      <c r="D27" s="162" t="n"/>
+      <c r="F27" s="163" t="n"/>
+      <c r="H27" s="163" t="n"/>
+      <c r="J27" s="163" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="162" t="n"/>
-      <c r="C28" s="162" t="n"/>
-      <c r="E28" s="163" t="n"/>
-      <c r="F28" s="164" t="n"/>
-      <c r="G28" s="164" t="n"/>
-      <c r="H28" s="165" t="n"/>
-      <c r="J28" s="162" t="n"/>
+      <c r="A28" s="160" t="n"/>
+      <c r="B28" s="161" t="n"/>
+      <c r="C28" s="161" t="n"/>
+      <c r="D28" s="162" t="n"/>
+      <c r="F28" s="163" t="n"/>
+      <c r="H28" s="163" t="n"/>
+      <c r="J28" s="163" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="166" t="n"/>
-      <c r="C29" s="166" t="n"/>
-      <c r="E29" s="167" t="n"/>
-      <c r="F29" s="168" t="n"/>
-      <c r="G29" s="168" t="n"/>
-      <c r="H29" s="169" t="n"/>
-      <c r="J29" s="166" t="n"/>
+      <c r="A29" s="164" t="n"/>
+      <c r="B29" s="165" t="n"/>
+      <c r="C29" s="165" t="n"/>
+      <c r="D29" s="166" t="n"/>
+      <c r="F29" s="167" t="n"/>
+      <c r="H29" s="167" t="n"/>
+      <c r="J29" s="167" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="170" t="inlineStr">
+      <c r="A30" s="168" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -6340,17 +6338,17 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="H1:J1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C1:G1"/>
     <mergeCell ref="A30:J30"/>
     <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A1:B2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="G5:G29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
+    <dataValidation sqref="C5:C29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
       <formula1>L_FAMILIAS</formula1>
     </dataValidation>
-    <dataValidation sqref="H5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
+    <dataValidation sqref="D5:D29" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor fora da lista" error="Escolha um item da lista." type="list" errorStyle="stop">
       <formula1>L_SETORES</formula1>
     </dataValidation>
   </dataValidations>
@@ -6396,7 +6394,7 @@
     <row r="1" ht="30.75" customHeight="1">
       <c r="A1" s="39" t="n"/>
       <c r="B1" s="40" t="n"/>
-      <c r="C1" s="171" t="inlineStr">
+      <c r="C1" s="169" t="inlineStr">
         <is>
           <t>Revisões</t>
         </is>
@@ -6422,246 +6420,246 @@
       <c r="E2" s="45" t="n"/>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="158" t="inlineStr">
+      <c r="A3" s="155" t="inlineStr">
         <is>
           <t>Rev</t>
         </is>
       </c>
-      <c r="B3" s="159" t="inlineStr">
+      <c r="B3" s="156" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="C3" s="159" t="inlineStr">
+      <c r="C3" s="156" t="inlineStr">
         <is>
           <t>Descrição da alteração</t>
         </is>
       </c>
-      <c r="D3" s="159" t="inlineStr">
+      <c r="D3" s="156" t="inlineStr">
         <is>
           <t>Elaborado por</t>
         </is>
       </c>
-      <c r="E3" s="160" t="inlineStr">
+      <c r="E3" s="157" t="inlineStr">
         <is>
           <t>Aprovado por</t>
         </is>
       </c>
     </row>
     <row r="4" hidden="1">
-      <c r="A4" s="161" t="inlineStr">
+      <c r="A4" s="159" t="inlineStr">
         <is>
           <t>revisao</t>
         </is>
       </c>
-      <c r="B4" s="161" t="inlineStr">
+      <c r="B4" s="159" t="inlineStr">
         <is>
           <t>data_revisao</t>
         </is>
       </c>
-      <c r="C4" s="161" t="inlineStr">
+      <c r="C4" s="159" t="inlineStr">
         <is>
           <t>descricao_alteracao</t>
         </is>
       </c>
-      <c r="D4" s="161" t="inlineStr">
+      <c r="D4" s="159" t="inlineStr">
         <is>
           <t>elaborado_por</t>
         </is>
       </c>
-      <c r="E4" s="161" t="inlineStr">
+      <c r="E4" s="159" t="inlineStr">
         <is>
           <t>aprovado_por</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="172" t="inlineStr">
+      <c r="A5" s="170" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B5" s="173" t="n">
+      <c r="B5" s="171" t="n">
         <v>46325</v>
       </c>
-      <c r="C5" s="174" t="inlineStr">
+      <c r="C5" s="172" t="inlineStr">
         <is>
           <t>Emissão inicial</t>
         </is>
       </c>
-      <c r="D5" s="164" t="n"/>
-      <c r="E5" s="165" t="n"/>
+      <c r="D5" s="161" t="n"/>
+      <c r="E5" s="162" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="172" t="n"/>
-      <c r="B6" s="173" t="n"/>
-      <c r="C6" s="174" t="n"/>
-      <c r="D6" s="164" t="n"/>
-      <c r="E6" s="165" t="n"/>
+      <c r="A6" s="170" t="n"/>
+      <c r="B6" s="171" t="n"/>
+      <c r="C6" s="172" t="n"/>
+      <c r="D6" s="161" t="n"/>
+      <c r="E6" s="162" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="172" t="n"/>
-      <c r="B7" s="173" t="n"/>
-      <c r="C7" s="174" t="n"/>
-      <c r="D7" s="164" t="n"/>
-      <c r="E7" s="165" t="n"/>
+      <c r="A7" s="170" t="n"/>
+      <c r="B7" s="171" t="n"/>
+      <c r="C7" s="172" t="n"/>
+      <c r="D7" s="161" t="n"/>
+      <c r="E7" s="162" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="172" t="n"/>
-      <c r="B8" s="173" t="n"/>
-      <c r="C8" s="174" t="n"/>
-      <c r="D8" s="164" t="n"/>
-      <c r="E8" s="165" t="n"/>
+      <c r="A8" s="170" t="n"/>
+      <c r="B8" s="171" t="n"/>
+      <c r="C8" s="172" t="n"/>
+      <c r="D8" s="161" t="n"/>
+      <c r="E8" s="162" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="172" t="n"/>
-      <c r="B9" s="173" t="n"/>
-      <c r="C9" s="174" t="n"/>
-      <c r="D9" s="164" t="n"/>
-      <c r="E9" s="165" t="n"/>
+      <c r="A9" s="170" t="n"/>
+      <c r="B9" s="171" t="n"/>
+      <c r="C9" s="172" t="n"/>
+      <c r="D9" s="161" t="n"/>
+      <c r="E9" s="162" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="172" t="n"/>
-      <c r="B10" s="173" t="n"/>
-      <c r="C10" s="174" t="n"/>
-      <c r="D10" s="164" t="n"/>
-      <c r="E10" s="165" t="n"/>
+      <c r="A10" s="170" t="n"/>
+      <c r="B10" s="171" t="n"/>
+      <c r="C10" s="172" t="n"/>
+      <c r="D10" s="161" t="n"/>
+      <c r="E10" s="162" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="172" t="n"/>
-      <c r="B11" s="173" t="n"/>
-      <c r="C11" s="174" t="n"/>
-      <c r="D11" s="164" t="n"/>
-      <c r="E11" s="165" t="n"/>
+      <c r="A11" s="170" t="n"/>
+      <c r="B11" s="171" t="n"/>
+      <c r="C11" s="172" t="n"/>
+      <c r="D11" s="161" t="n"/>
+      <c r="E11" s="162" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="172" t="n"/>
-      <c r="B12" s="173" t="n"/>
-      <c r="C12" s="174" t="n"/>
-      <c r="D12" s="164" t="n"/>
-      <c r="E12" s="165" t="n"/>
+      <c r="A12" s="170" t="n"/>
+      <c r="B12" s="171" t="n"/>
+      <c r="C12" s="172" t="n"/>
+      <c r="D12" s="161" t="n"/>
+      <c r="E12" s="162" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="172" t="n"/>
-      <c r="B13" s="173" t="n"/>
-      <c r="C13" s="174" t="n"/>
-      <c r="D13" s="164" t="n"/>
-      <c r="E13" s="165" t="n"/>
+      <c r="A13" s="170" t="n"/>
+      <c r="B13" s="171" t="n"/>
+      <c r="C13" s="172" t="n"/>
+      <c r="D13" s="161" t="n"/>
+      <c r="E13" s="162" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="172" t="n"/>
-      <c r="B14" s="173" t="n"/>
-      <c r="C14" s="174" t="n"/>
-      <c r="D14" s="164" t="n"/>
-      <c r="E14" s="165" t="n"/>
+      <c r="A14" s="170" t="n"/>
+      <c r="B14" s="171" t="n"/>
+      <c r="C14" s="172" t="n"/>
+      <c r="D14" s="161" t="n"/>
+      <c r="E14" s="162" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="172" t="n"/>
-      <c r="B15" s="173" t="n"/>
-      <c r="C15" s="174" t="n"/>
-      <c r="D15" s="164" t="n"/>
-      <c r="E15" s="165" t="n"/>
+      <c r="A15" s="170" t="n"/>
+      <c r="B15" s="171" t="n"/>
+      <c r="C15" s="172" t="n"/>
+      <c r="D15" s="161" t="n"/>
+      <c r="E15" s="162" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="172" t="n"/>
-      <c r="B16" s="173" t="n"/>
-      <c r="C16" s="174" t="n"/>
-      <c r="D16" s="164" t="n"/>
-      <c r="E16" s="165" t="n"/>
+      <c r="A16" s="170" t="n"/>
+      <c r="B16" s="171" t="n"/>
+      <c r="C16" s="172" t="n"/>
+      <c r="D16" s="161" t="n"/>
+      <c r="E16" s="162" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="172" t="n"/>
-      <c r="B17" s="173" t="n"/>
-      <c r="C17" s="174" t="n"/>
-      <c r="D17" s="164" t="n"/>
-      <c r="E17" s="165" t="n"/>
+      <c r="A17" s="170" t="n"/>
+      <c r="B17" s="171" t="n"/>
+      <c r="C17" s="172" t="n"/>
+      <c r="D17" s="161" t="n"/>
+      <c r="E17" s="162" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="172" t="n"/>
-      <c r="B18" s="173" t="n"/>
-      <c r="C18" s="174" t="n"/>
-      <c r="D18" s="164" t="n"/>
-      <c r="E18" s="165" t="n"/>
+      <c r="A18" s="170" t="n"/>
+      <c r="B18" s="171" t="n"/>
+      <c r="C18" s="172" t="n"/>
+      <c r="D18" s="161" t="n"/>
+      <c r="E18" s="162" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="172" t="n"/>
-      <c r="B19" s="173" t="n"/>
-      <c r="C19" s="174" t="n"/>
-      <c r="D19" s="164" t="n"/>
-      <c r="E19" s="165" t="n"/>
+      <c r="A19" s="170" t="n"/>
+      <c r="B19" s="171" t="n"/>
+      <c r="C19" s="172" t="n"/>
+      <c r="D19" s="161" t="n"/>
+      <c r="E19" s="162" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="172" t="n"/>
-      <c r="B20" s="173" t="n"/>
-      <c r="C20" s="174" t="n"/>
-      <c r="D20" s="164" t="n"/>
-      <c r="E20" s="165" t="n"/>
+      <c r="A20" s="170" t="n"/>
+      <c r="B20" s="171" t="n"/>
+      <c r="C20" s="172" t="n"/>
+      <c r="D20" s="161" t="n"/>
+      <c r="E20" s="162" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="172" t="n"/>
-      <c r="B21" s="173" t="n"/>
-      <c r="C21" s="174" t="n"/>
-      <c r="D21" s="164" t="n"/>
-      <c r="E21" s="165" t="n"/>
+      <c r="A21" s="170" t="n"/>
+      <c r="B21" s="171" t="n"/>
+      <c r="C21" s="172" t="n"/>
+      <c r="D21" s="161" t="n"/>
+      <c r="E21" s="162" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="172" t="n"/>
-      <c r="B22" s="173" t="n"/>
-      <c r="C22" s="174" t="n"/>
-      <c r="D22" s="164" t="n"/>
-      <c r="E22" s="165" t="n"/>
+      <c r="A22" s="170" t="n"/>
+      <c r="B22" s="171" t="n"/>
+      <c r="C22" s="172" t="n"/>
+      <c r="D22" s="161" t="n"/>
+      <c r="E22" s="162" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="172" t="n"/>
-      <c r="B23" s="173" t="n"/>
-      <c r="C23" s="174" t="n"/>
-      <c r="D23" s="164" t="n"/>
-      <c r="E23" s="165" t="n"/>
+      <c r="A23" s="170" t="n"/>
+      <c r="B23" s="171" t="n"/>
+      <c r="C23" s="172" t="n"/>
+      <c r="D23" s="161" t="n"/>
+      <c r="E23" s="162" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="172" t="n"/>
-      <c r="B24" s="173" t="n"/>
-      <c r="C24" s="174" t="n"/>
-      <c r="D24" s="164" t="n"/>
-      <c r="E24" s="165" t="n"/>
+      <c r="A24" s="170" t="n"/>
+      <c r="B24" s="171" t="n"/>
+      <c r="C24" s="172" t="n"/>
+      <c r="D24" s="161" t="n"/>
+      <c r="E24" s="162" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="172" t="n"/>
-      <c r="B25" s="173" t="n"/>
-      <c r="C25" s="174" t="n"/>
-      <c r="D25" s="164" t="n"/>
-      <c r="E25" s="165" t="n"/>
+      <c r="A25" s="170" t="n"/>
+      <c r="B25" s="171" t="n"/>
+      <c r="C25" s="172" t="n"/>
+      <c r="D25" s="161" t="n"/>
+      <c r="E25" s="162" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="172" t="n"/>
-      <c r="B26" s="173" t="n"/>
-      <c r="C26" s="174" t="n"/>
-      <c r="D26" s="164" t="n"/>
-      <c r="E26" s="165" t="n"/>
+      <c r="A26" s="170" t="n"/>
+      <c r="B26" s="171" t="n"/>
+      <c r="C26" s="172" t="n"/>
+      <c r="D26" s="161" t="n"/>
+      <c r="E26" s="162" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="172" t="n"/>
-      <c r="B27" s="173" t="n"/>
-      <c r="C27" s="174" t="n"/>
-      <c r="D27" s="164" t="n"/>
-      <c r="E27" s="165" t="n"/>
+      <c r="A27" s="170" t="n"/>
+      <c r="B27" s="171" t="n"/>
+      <c r="C27" s="172" t="n"/>
+      <c r="D27" s="161" t="n"/>
+      <c r="E27" s="162" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="172" t="n"/>
-      <c r="B28" s="173" t="n"/>
-      <c r="C28" s="174" t="n"/>
-      <c r="D28" s="164" t="n"/>
-      <c r="E28" s="165" t="n"/>
+      <c r="A28" s="170" t="n"/>
+      <c r="B28" s="171" t="n"/>
+      <c r="C28" s="172" t="n"/>
+      <c r="D28" s="161" t="n"/>
+      <c r="E28" s="162" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="175" t="n"/>
-      <c r="B29" s="176" t="n"/>
-      <c r="C29" s="177" t="n"/>
-      <c r="D29" s="168" t="n"/>
-      <c r="E29" s="169" t="n"/>
+      <c r="A29" s="173" t="n"/>
+      <c r="B29" s="174" t="n"/>
+      <c r="C29" s="175" t="n"/>
+      <c r="D29" s="165" t="n"/>
+      <c r="E29" s="166" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="170" t="inlineStr">
+      <c r="A30" s="168" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
